--- a/data/analysis_panns/sound_class_eval_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_panns/sound_class_eval_panns_w2_5s_h1_25s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="25">
   <si>
     <t>class</t>
   </si>
@@ -54,18 +54,6 @@
     <t>support</t>
   </si>
   <si>
-    <t>animal</t>
-  </si>
-  <si>
-    <t>breaking</t>
-  </si>
-  <si>
-    <t>burst_pop</t>
-  </si>
-  <si>
-    <t>door</t>
-  </si>
-  <si>
     <t>engine</t>
   </si>
   <si>
@@ -78,34 +66,13 @@
     <t>horn</t>
   </si>
   <si>
-    <t>horse</t>
-  </si>
-  <si>
     <t>impact</t>
   </si>
   <si>
-    <t>music</t>
-  </si>
-  <si>
     <t>shout</t>
   </si>
   <si>
-    <t>shuffle</t>
-  </si>
-  <si>
-    <t>sigh</t>
-  </si>
-  <si>
-    <t>silence</t>
-  </si>
-  <si>
     <t>skidding</t>
-  </si>
-  <si>
-    <t>speech</t>
-  </si>
-  <si>
-    <t>tick_tock</t>
   </si>
   <si>
     <t>tire_squeal</t>
@@ -493,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -527,25 +494,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>5</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -553,25 +520,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -579,16 +546,16 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -597,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -605,25 +572,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -631,25 +598,25 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -657,22 +624,22 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -683,25 +650,25 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>0.714</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="D8">
-        <v>0.769</v>
+        <v>0.8</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -709,310 +676,24 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>8</v>
-      </c>
-      <c r="H11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>0.667</v>
-      </c>
-      <c r="D17">
-        <v>0.8</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-      <c r="H20">
         <v>5</v>
       </c>
     </row>
@@ -1028,31 +709,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1060,7 +741,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>93</v>
@@ -1069,7 +750,7 @@
         <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>60</v>
@@ -1089,7 +770,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>132</v>
@@ -1098,7 +779,7 @@
         <v>208</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -1125,31 +806,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1157,7 +838,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>95</v>
@@ -1166,7 +847,7 @@
         <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>60</v>
@@ -1186,7 +867,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>189</v>
@@ -1195,7 +876,7 @@
         <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -1222,31 +903,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1254,7 +935,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>88</v>
@@ -1263,7 +944,7 @@
         <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>60</v>
@@ -1283,7 +964,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>169</v>
@@ -1292,7 +973,7 @@
         <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -1319,31 +1000,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1351,7 +1032,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>19</v>
@@ -1360,7 +1041,7 @@
         <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1380,7 +1061,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>73</v>
@@ -1389,7 +1070,7 @@
         <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1409,7 +1090,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>79</v>
@@ -1418,16 +1099,16 @@
         <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H4">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1445,31 +1126,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1477,7 +1158,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>31</v>
@@ -1486,7 +1167,7 @@
         <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1506,7 +1187,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>53</v>
@@ -1515,7 +1196,7 @@
         <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1535,7 +1216,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>63</v>
@@ -1544,7 +1225,7 @@
         <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>60</v>
@@ -1571,31 +1252,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1603,7 +1284,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1612,7 +1293,7 @@
         <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -1632,7 +1313,7 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>53</v>
@@ -1641,7 +1322,7 @@
         <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>30</v>
@@ -1661,7 +1342,7 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>74</v>
@@ -1670,7 +1351,7 @@
         <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -1697,31 +1378,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1729,7 +1410,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1737,17 +1418,8 @@
       <c r="D2">
         <v>36</v>
       </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>90</v>
-      </c>
       <c r="H2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1758,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>36</v>
@@ -1766,17 +1438,8 @@
       <c r="D3">
         <v>40</v>
       </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>90</v>
-      </c>
       <c r="H3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1794,31 +1457,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1826,7 +1489,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1834,17 +1497,8 @@
       <c r="D2">
         <v>44</v>
       </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>210</v>
-      </c>
       <c r="H2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1855,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>44</v>
@@ -1863,17 +1517,8 @@
       <c r="D3">
         <v>123</v>
       </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>210</v>
-      </c>
       <c r="H3">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1891,31 +1536,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1923,7 +1568,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1931,17 +1576,8 @@
       <c r="D2">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>210</v>
-      </c>
       <c r="H2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1952,7 +1588,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -1960,17 +1596,8 @@
       <c r="D3">
         <v>72</v>
       </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>210</v>
-      </c>
       <c r="H3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1988,31 +1615,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2020,7 +1647,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>96</v>
@@ -2029,19 +1656,19 @@
         <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G2">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H2">
         <v>9</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2049,7 +1676,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>116</v>
@@ -2058,16 +1685,16 @@
         <v>160</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G3">
         <v>180</v>
       </c>
       <c r="H3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -2085,31 +1712,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2117,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>60</v>
@@ -2132,13 +1759,13 @@
         <v>30</v>
       </c>
       <c r="G2">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H2">
         <v>17</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2153,31 +1780,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2185,7 +1812,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>114</v>
@@ -2194,19 +1821,19 @@
         <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="G2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2221,31 +1848,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2253,7 +1880,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>14</v>
@@ -2262,7 +1889,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2289,31 +1916,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2321,7 +1948,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>37</v>
@@ -2330,7 +1957,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>0</v>

--- a/data/analysis_panns/sound_class_eval_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_panns/sound_class_eval_panns_w2_5s_h1_25s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="25">
   <si>
     <t>class</t>
   </si>
@@ -1371,6 +1377,378 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>37</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>52</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>122</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>108</v>
+      </c>
+      <c r="D2">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>90</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>30</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>138</v>
+      </c>
+      <c r="D3">
+        <v>240</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>90</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>102</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>103</v>
+      </c>
+      <c r="D2">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>60</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>35</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>138</v>
+      </c>
+      <c r="D3">
+        <v>182</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>44</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I3"/>
@@ -1440,6 +1818,200 @@
       </c>
       <c r="H3">
         <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>90</v>
+      </c>
+      <c r="H2">
+        <v>34</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>63</v>
+      </c>
+      <c r="D3">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>90</v>
+      </c>
+      <c r="H3">
+        <v>27</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>90</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>90</v>
+      </c>
+      <c r="H3">
+        <v>40</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
